--- a/测试用例导入模板.xlsx
+++ b/测试用例导入模板.xlsx
@@ -65952,7 +65952,19 @@
 涉及省份：广东
 测试前提：无
 测试场景：无
-测试要点：在表单页面“借阅明细清单”下，新增“手工补录清单”，可手工添加银行回单明细信息，可添加多条手工补录清单，可逐条删除。表单字段包括：本方账户，金额，回单所属开始日期，回单所属期间结束日期，对方户名，对方账户，接收回单邮箱。本方账户：下拉框，可选内容见下文第2点方案；金额：文本框；回单所属开始日期、回单所属期间结束日期：日期选择框；对方户名：文本框；对方账户：文本框；接收回单邮箱：文本框；在“系统管理 &gt; 业务数据配置 &gt; 银行账户配置”，新增页面和查询结果表格新增提交字段，“是否可借阅”，配置为是的银行账户，可在银行回单借阅明细流程的“本方账户”下拉框选择（包括“借阅明细清单”和“手工补录清单”），不配置或配置为“否”的不可选择；广东电子回单调阅流程（PROC-HDDY-09），新增“分公司财务审核”环节退回“申请人发起”路由；“借阅明细清单”可多次增加借阅明细（目前可一次添加多条，但不能多次增加）；屏蔽“借阅明细清单”上“添加”按钮旁边的红字和模板下载功能；提交表单时，增加校验，“借阅明细清单”或“手工补录清单”必须任一不为空方可提交；在“档案查询 &gt; 清册查询”新增“电子回单调阅”页签，查询条件按“档案调阅”查询条件，查询结果结果按“附件电子归档”，可查询电子回单调阅流程，点击流程号可查看流程表单。</v>
+测试要点：1. 在表单页面“借阅明细清单”下，新增“手工补录清单”，可手工添加银行回单明细信息，可添加多条手工补录清单，可逐条删除。表单字段包括：本方账户，金额，回单所属开始日期，回单所属期间结束日期，对方户名，对方账户，接收回单邮箱。
+2. 本方账户：下拉框，可选内容见下文第2点方案；
+3. 金额：文本框；
+4. 回单所属开始日期、回单所属期间结束日期：日期选择框；
+5. 对方户名：文本框；
+6. 对方账户：文本框；
+7. 接收回单邮箱：文本框；
+8. 在“系统管理 &gt; 业务数据配置 &gt; 银行账户配置”，新增页面和查询结果表格新增提交字段，“是否可借阅”，配置为是的银行账户，可在银行回单借阅明细流程的“本方账户”下拉框选择（包括“借阅明细清单”和“手工补录清单”），不配置或配置为“否”的不可选择；
+9. 广东电子回单调阅流程（PROC-HDDY-09），新增“分公司财务审核”环节退回“申请人发起”路由；
+10. “借阅明细清单”可多次增加借阅明细（目前可一次添加多条，但不能多次增加）；
+11. 屏蔽“借阅明细清单”上“添加”按钮旁边的红字和模板下载功能；
+12. 提交表单时，增加校验，“借阅明细清单”或“手工补录清单”必须任一不为空方可提交；
+13. 在“档案查询 &gt; 清册查询”新增“电子回单调阅”页签，查询条件按“档案调阅”查询条件，查询结果结果按“附件电子归档”，可查询电子回单调阅流程，点击流程号可查看流程表单。</v>
       </c>
       <c r="I2" t="str">
         <v/>
@@ -66050,7 +66062,9 @@
 涉及省份：集团
 测试前提：无
 测试场景：无
-测试要点：在“档案查询 &gt; 其他电子档案查看 &gt; 税务资料查看”菜单：增加省份下拉框，当登录账号省编为总部时，可选择其他省份，非总部时，仅可选择账号所属省份；选择不同省份时，后台进入不同节点数据库查询对应税务资料目录，查询的税务资料附件可查看可下载，但不可删除。</v>
+测试要点：1. 在“档案查询 &gt; 其他电子档案查看 &gt; 税务资料查看”菜单：
+2. 增加省份下拉框，当登录账号省编为总部时，可选择其他省份，非总部时，仅可选择账号所属省份；
+3. 选择不同省份时，后台进入不同节点数据库查询对应税务资料目录，查询的税务资料附件可查看可下载，但不可删除。</v>
       </c>
       <c r="I4" t="str">
         <v/>
